--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/12.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/12.xlsx
@@ -426,13 +426,13 @@
         <v>-7.158916415155779</v>
       </c>
       <c r="E2">
-        <v>-5.782315439147721</v>
+        <v>-7.459648626166798</v>
       </c>
       <c r="F2">
-        <v>-7.044407547795405</v>
+        <v>-7.097657489549566</v>
       </c>
       <c r="G2">
-        <v>-12.02230355580582</v>
+        <v>-13.2082369737934</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.312649944504068</v>
       </c>
       <c r="E3">
-        <v>-6.79136813143286</v>
+        <v>-8.543480009740598</v>
       </c>
       <c r="F3">
-        <v>-6.956935263529389</v>
+        <v>-6.841320025120662</v>
       </c>
       <c r="G3">
-        <v>-11.73872553545739</v>
+        <v>-12.94533662088325</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.661284953802317</v>
       </c>
       <c r="E4">
-        <v>-8.289052226093647</v>
+        <v>-7.532108738763531</v>
       </c>
       <c r="F4">
-        <v>-7.176924794690853</v>
+        <v>-6.762848781053465</v>
       </c>
       <c r="G4">
-        <v>-11.73167738400428</v>
+        <v>-13.23111284346976</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.96325054104141</v>
       </c>
       <c r="E5">
-        <v>-7.941392219576778</v>
+        <v>-9.20422965219978</v>
       </c>
       <c r="F5">
-        <v>-6.820836984351638</v>
+        <v>-6.453436988759793</v>
       </c>
       <c r="G5">
-        <v>-11.63941247982479</v>
+        <v>-12.88514428188822</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.1639973603672</v>
       </c>
       <c r="E6">
-        <v>-9.046729326213004</v>
+        <v>-10.27112454298489</v>
       </c>
       <c r="F6">
-        <v>-7.334157211416228</v>
+        <v>-6.506527883972616</v>
       </c>
       <c r="G6">
-        <v>-11.74538304253686</v>
+        <v>-12.96857665056894</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.14821107439195</v>
       </c>
       <c r="E7">
-        <v>-9.407947583908838</v>
+        <v>-10.84771702448553</v>
       </c>
       <c r="F7">
-        <v>-7.097039527467078</v>
+        <v>-6.52881013874052</v>
       </c>
       <c r="G7">
-        <v>-10.57610166861182</v>
+        <v>-12.50709653403115</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.8458173461896</v>
       </c>
       <c r="E8">
-        <v>-10.36648967711242</v>
+        <v>-11.24759033631084</v>
       </c>
       <c r="F8">
-        <v>-7.109766978427391</v>
+        <v>-6.692773868981043</v>
       </c>
       <c r="G8">
-        <v>-11.3610055316087</v>
+        <v>-12.38250415266068</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.1767800977169</v>
       </c>
       <c r="E9">
-        <v>-10.22715306037041</v>
+        <v>-11.8574942726119</v>
       </c>
       <c r="F9">
-        <v>-6.304411622077655</v>
+        <v>-6.315116199840332</v>
       </c>
       <c r="G9">
-        <v>-11.30192222536933</v>
+        <v>-12.99530930579855</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.0925150918742</v>
       </c>
       <c r="E10">
-        <v>-11.36314793603857</v>
+        <v>-12.07151448268841</v>
       </c>
       <c r="F10">
-        <v>-5.98714566425434</v>
+        <v>-6.349468596034427</v>
       </c>
       <c r="G10">
-        <v>-10.77532367807408</v>
+        <v>-12.34483014442377</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.55677224504844</v>
       </c>
       <c r="E11">
-        <v>-12.45828239073551</v>
+        <v>-13.5778253203338</v>
       </c>
       <c r="F11">
-        <v>-6.218503709651825</v>
+        <v>-5.96071577390062</v>
       </c>
       <c r="G11">
-        <v>-10.45989489909232</v>
+        <v>-12.13665641982332</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.56945387388975</v>
       </c>
       <c r="E12">
-        <v>-11.72767197976</v>
+        <v>-13.63542298123736</v>
       </c>
       <c r="F12">
-        <v>-6.248510076267134</v>
+        <v>-5.874979747710871</v>
       </c>
       <c r="G12">
-        <v>-9.420446500126413</v>
+        <v>-11.23451620764423</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.1578050823145</v>
       </c>
       <c r="E13">
-        <v>-13.08753196799734</v>
+        <v>-14.18589522466176</v>
       </c>
       <c r="F13">
-        <v>-6.142018890616542</v>
+        <v>-5.84989926785631</v>
       </c>
       <c r="G13">
-        <v>-9.749134013992952</v>
+        <v>-11.17313869334614</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.39224378180363</v>
       </c>
       <c r="E14">
-        <v>-13.99961191788223</v>
+        <v>-15.36919906828804</v>
       </c>
       <c r="F14">
-        <v>-6.073190671485333</v>
+        <v>-5.41085791743335</v>
       </c>
       <c r="G14">
-        <v>-9.232066527305266</v>
+        <v>-10.75296425350184</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.370261773973696</v>
       </c>
       <c r="E15">
-        <v>-13.97861791238267</v>
+        <v>-14.77728675921946</v>
       </c>
       <c r="F15">
-        <v>-5.516580792317845</v>
+        <v>-5.558554996985099</v>
       </c>
       <c r="G15">
-        <v>-9.618519750286548</v>
+        <v>-10.52404002946124</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.20567654975473</v>
       </c>
       <c r="E16">
-        <v>-15.00742380828927</v>
+        <v>-16.32988765817126</v>
       </c>
       <c r="F16">
-        <v>-5.106940686122448</v>
+        <v>-5.490955246712242</v>
       </c>
       <c r="G16">
-        <v>-8.42281691241258</v>
+        <v>-10.50969212509404</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.01807411368207</v>
       </c>
       <c r="E17">
-        <v>-14.96839289081715</v>
+        <v>-17.53493270550837</v>
       </c>
       <c r="F17">
-        <v>-5.161355312444944</v>
+        <v>-5.006749648753847</v>
       </c>
       <c r="G17">
-        <v>-8.185354791426198</v>
+        <v>-9.523944085320649</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.932563862087565</v>
       </c>
       <c r="E18">
-        <v>-16.12053177632265</v>
+        <v>-17.89213420675941</v>
       </c>
       <c r="F18">
-        <v>-4.859631598016655</v>
+        <v>-4.511589720260831</v>
       </c>
       <c r="G18">
-        <v>-7.945403140194283</v>
+        <v>-9.39679596279386</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.9368924483882631</v>
       </c>
       <c r="E19">
-        <v>-17.04558580423952</v>
+        <v>-18.64010225860632</v>
       </c>
       <c r="F19">
-        <v>-4.452633155468785</v>
+        <v>-4.07408084953305</v>
       </c>
       <c r="G19">
-        <v>-7.21772867793478</v>
+        <v>-9.686809683670633</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.497066878455362</v>
       </c>
       <c r="E20">
-        <v>-18.44186378044654</v>
+        <v>-19.05285002203544</v>
       </c>
       <c r="F20">
-        <v>-4.097307443140146</v>
+        <v>-4.269613661494263</v>
       </c>
       <c r="G20">
-        <v>-7.772821090686536</v>
+        <v>-9.763690482729128</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.677889842155175</v>
       </c>
       <c r="E21">
-        <v>-17.89532678093481</v>
+        <v>-21.09858362652651</v>
       </c>
       <c r="F21">
-        <v>-4.097639618468668</v>
+        <v>-3.652354862930808</v>
       </c>
       <c r="G21">
-        <v>-7.615517208842526</v>
+        <v>-9.606095272877663</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.436440100499132</v>
       </c>
       <c r="E22">
-        <v>-18.67321898902441</v>
+        <v>-20.43372665814237</v>
       </c>
       <c r="F22">
-        <v>-3.823633905705453</v>
+        <v>-3.569862723490422</v>
       </c>
       <c r="G22">
-        <v>-8.425567975755715</v>
+        <v>-9.102945319637071</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.765431053422133</v>
       </c>
       <c r="E23">
-        <v>-19.13360177054021</v>
+        <v>-21.420630584056</v>
       </c>
       <c r="F23">
-        <v>-3.872684853094823</v>
+        <v>-3.52643307729645</v>
       </c>
       <c r="G23">
-        <v>-8.274014511513419</v>
+        <v>-8.977459090970996</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.686856479883152</v>
       </c>
       <c r="E24">
-        <v>-19.33072171562009</v>
+        <v>-21.06452044504081</v>
       </c>
       <c r="F24">
-        <v>-3.341314500323233</v>
+        <v>-3.29901226216447</v>
       </c>
       <c r="G24">
-        <v>-8.451969576431402</v>
+        <v>-9.261000695318495</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.23985352408659</v>
       </c>
       <c r="E25">
-        <v>-20.07889807727136</v>
+        <v>-21.28220871906354</v>
       </c>
       <c r="F25">
-        <v>-3.295529805603101</v>
+        <v>-3.605277915062309</v>
       </c>
       <c r="G25">
-        <v>-8.258286109656341</v>
+        <v>-10.02230698971145</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.478999475451261</v>
       </c>
       <c r="E26">
-        <v>-21.41353446528598</v>
+        <v>-21.53718897653942</v>
       </c>
       <c r="F26">
-        <v>-3.326642456884848</v>
+        <v>-3.166775003451169</v>
       </c>
       <c r="G26">
-        <v>-7.764895644665521</v>
+        <v>-9.69682077338139</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.468377567331446</v>
       </c>
       <c r="E27">
-        <v>-20.75499018966853</v>
+        <v>-21.47256765244997</v>
       </c>
       <c r="F27">
-        <v>-3.173246209601838</v>
+        <v>-3.075124434005431</v>
       </c>
       <c r="G27">
-        <v>-9.703809335014791</v>
+        <v>-9.410882334063459</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.275199734331806</v>
       </c>
       <c r="E28">
-        <v>-21.14322079482012</v>
+        <v>-21.90275004080861</v>
       </c>
       <c r="F28">
-        <v>-2.798044649810427</v>
+        <v>-3.560945348399285</v>
       </c>
       <c r="G28">
-        <v>-9.494480230021134</v>
+        <v>-9.739238793376071</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.0316847096420174</v>
       </c>
       <c r="E29">
-        <v>-20.06255481457768</v>
+        <v>-21.19112299287325</v>
       </c>
       <c r="F29">
-        <v>-2.943030482852814</v>
+        <v>-3.322084779434645</v>
       </c>
       <c r="G29">
-        <v>-8.869578343482766</v>
+        <v>-9.335295958310819</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.380795054612136</v>
       </c>
       <c r="E30">
-        <v>-19.33088474068437</v>
+        <v>-21.74000574192096</v>
       </c>
       <c r="F30">
-        <v>-3.387754433658979</v>
+        <v>-3.301613335809261</v>
       </c>
       <c r="G30">
-        <v>-9.208555032885361</v>
+        <v>-10.62856388377265</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.709069306071317</v>
       </c>
       <c r="E31">
-        <v>-19.35618079649122</v>
+        <v>-21.83645770981033</v>
       </c>
       <c r="F31">
-        <v>-3.119774265383727</v>
+        <v>-3.440623326407851</v>
       </c>
       <c r="G31">
-        <v>-9.095473418354935</v>
+        <v>-9.676027236849228</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.963345016362067</v>
       </c>
       <c r="E32">
-        <v>-19.09261455229679</v>
+        <v>-20.82478303107474</v>
       </c>
       <c r="F32">
-        <v>-3.39411381021027</v>
+        <v>-3.638066353599919</v>
       </c>
       <c r="G32">
-        <v>-9.437651405294005</v>
+        <v>-9.656521502531842</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.094983146169699</v>
       </c>
       <c r="E33">
-        <v>-18.44171434080429</v>
+        <v>-21.16112638104645</v>
       </c>
       <c r="F33">
-        <v>-3.642960348215659</v>
+        <v>-3.346767642935862</v>
       </c>
       <c r="G33">
-        <v>-8.998987568612877</v>
+        <v>-9.806389899094649</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.060803904525594</v>
       </c>
       <c r="E34">
-        <v>-18.12254749274368</v>
+        <v>-20.5129160831145</v>
       </c>
       <c r="F34">
-        <v>-3.591780496601094</v>
+        <v>-3.193415299125201</v>
       </c>
       <c r="G34">
-        <v>-8.777962306228975</v>
+        <v>-8.780670332480099</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.826272864336296</v>
       </c>
       <c r="E35">
-        <v>-19.04673658212508</v>
+        <v>-19.8402293831711</v>
       </c>
       <c r="F35">
-        <v>-3.292134327619026</v>
+        <v>-3.551228598764447</v>
       </c>
       <c r="G35">
-        <v>-8.899277247515569</v>
+        <v>-9.449082719041108</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.360586139422917</v>
       </c>
       <c r="E36">
-        <v>-17.24104832783259</v>
+        <v>-18.93675353390079</v>
       </c>
       <c r="F36">
-        <v>-3.267298216148292</v>
+        <v>-3.625154590892484</v>
       </c>
       <c r="G36">
-        <v>-8.538689316832611</v>
+        <v>-9.480281300203201</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.641862442668627</v>
       </c>
       <c r="E37">
-        <v>-17.40378356977223</v>
+        <v>-19.11618525950671</v>
       </c>
       <c r="F37">
-        <v>-4.004273500131733</v>
+        <v>-3.589526508898077</v>
       </c>
       <c r="G37">
-        <v>-8.623293618634225</v>
+        <v>-8.466602187714981</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.661571834634548</v>
       </c>
       <c r="E38">
-        <v>-16.47970316376702</v>
+        <v>-18.7560402501507</v>
       </c>
       <c r="F38">
-        <v>-3.217630963411239</v>
+        <v>-3.237026357780386</v>
       </c>
       <c r="G38">
-        <v>-8.16580933056234</v>
+        <v>-8.485651066747947</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.424120893961655</v>
       </c>
       <c r="E39">
-        <v>-16.53302594520734</v>
+        <v>-18.51491259466427</v>
       </c>
       <c r="F39">
-        <v>-3.289340244369384</v>
+        <v>-3.659726504448321</v>
       </c>
       <c r="G39">
-        <v>-8.418066279563726</v>
+        <v>-8.340467092123209</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.945838117149178</v>
       </c>
       <c r="E40">
-        <v>-16.60663176172801</v>
+        <v>-18.75566438680806</v>
       </c>
       <c r="F40">
-        <v>-3.774346873606286</v>
+        <v>-3.480313722145587</v>
       </c>
       <c r="G40">
-        <v>-7.581130572326116</v>
+        <v>-7.728674965920355</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.256943076154918</v>
       </c>
       <c r="E41">
-        <v>-15.46944589739584</v>
+        <v>-17.76386518049214</v>
       </c>
       <c r="F41">
-        <v>-3.209194869781129</v>
+        <v>-3.704903177494797</v>
       </c>
       <c r="G41">
-        <v>-6.736176723792393</v>
+        <v>-7.768100252747535</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.398593208492574</v>
       </c>
       <c r="E42">
-        <v>-14.71266996360401</v>
+        <v>-17.44989249211833</v>
       </c>
       <c r="F42">
-        <v>-3.645383322868847</v>
+        <v>-3.593642666522587</v>
       </c>
       <c r="G42">
-        <v>-7.365564399536473</v>
+        <v>-7.832705548946413</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.418409905708576</v>
       </c>
       <c r="E43">
-        <v>-13.69911143968124</v>
+        <v>-16.41756344343377</v>
       </c>
       <c r="F43">
-        <v>-3.51061457337259</v>
+        <v>-3.610253918050926</v>
       </c>
       <c r="G43">
-        <v>-6.656193943563601</v>
+        <v>-7.744628484874103</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.373391988175245</v>
       </c>
       <c r="E44">
-        <v>-14.20573446928936</v>
+        <v>-16.20931250924303</v>
       </c>
       <c r="F44">
-        <v>-3.843819562576872</v>
+        <v>-3.835836585916093</v>
       </c>
       <c r="G44">
-        <v>-6.27931481828189</v>
+        <v>-7.525404159263565</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.324802919815826</v>
       </c>
       <c r="E45">
-        <v>-13.33737693594853</v>
+        <v>-16.00806259586815</v>
       </c>
       <c r="F45">
-        <v>-4.358472632792565</v>
+        <v>-3.929843860622795</v>
       </c>
       <c r="G45">
-        <v>-7.144664937883064</v>
+        <v>-7.328386973130458</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.335669481341177</v>
       </c>
       <c r="E46">
-        <v>-12.96070299646452</v>
+        <v>-15.54489933131165</v>
       </c>
       <c r="F46">
-        <v>-4.097764701946491</v>
+        <v>-3.743726272561802</v>
       </c>
       <c r="G46">
-        <v>-6.437923055068373</v>
+        <v>-7.356712000764462</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.4670466002322959</v>
       </c>
       <c r="E47">
-        <v>-13.12732819757675</v>
+        <v>-15.09619548426163</v>
       </c>
       <c r="F47">
-        <v>-4.153015150978413</v>
+        <v>-4.014128587122839</v>
       </c>
       <c r="G47">
-        <v>-6.924530212249226</v>
+        <v>-7.275471213230747</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.2238881900983524</v>
       </c>
       <c r="E48">
-        <v>-11.28141350867413</v>
+        <v>-14.05226448516941</v>
       </c>
       <c r="F48">
-        <v>-4.300310472339803</v>
+        <v>-4.345826776021428</v>
       </c>
       <c r="G48">
-        <v>-7.522345215185278</v>
+        <v>-7.214169841480063</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.6948299111342586</v>
       </c>
       <c r="E49">
-        <v>-10.53143481436781</v>
+        <v>-14.50052907024068</v>
       </c>
       <c r="F49">
-        <v>-4.23747549136785</v>
+        <v>-4.105607684516197</v>
       </c>
       <c r="G49">
-        <v>-6.396630620557043</v>
+        <v>-7.190913259066683</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.9182672552495637</v>
       </c>
       <c r="E50">
-        <v>-11.89383074804944</v>
+        <v>-13.45288925093619</v>
       </c>
       <c r="F50">
-        <v>-4.369233953722333</v>
+        <v>-4.169522856581401</v>
       </c>
       <c r="G50">
-        <v>-6.938030616958375</v>
+        <v>-6.716008880367152</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.8835704464616099</v>
       </c>
       <c r="E51">
-        <v>-11.15272786279816</v>
+        <v>-13.31982909916881</v>
       </c>
       <c r="F51">
-        <v>-4.651015551295628</v>
+        <v>-4.360550178238786</v>
       </c>
       <c r="G51">
-        <v>-6.677215907737972</v>
+        <v>-6.807631538712021</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.5965255684444777</v>
       </c>
       <c r="E52">
-        <v>-10.98671853415097</v>
+        <v>-12.58819978154157</v>
       </c>
       <c r="F52">
-        <v>-4.697761152203006</v>
+        <v>-4.279959970355228</v>
       </c>
       <c r="G52">
-        <v>-5.945148351547856</v>
+        <v>-7.165518064234933</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.07988609962736366</v>
       </c>
       <c r="E53">
-        <v>-10.83047712393833</v>
+        <v>-11.77032567643825</v>
       </c>
       <c r="F53">
-        <v>-4.493911531517687</v>
+        <v>-4.188666427260097</v>
       </c>
       <c r="G53">
-        <v>-6.010733569226358</v>
+        <v>-7.144827154614489</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.6335248376480643</v>
       </c>
       <c r="E54">
-        <v>-10.8005257968516</v>
+        <v>-12.34021148793352</v>
       </c>
       <c r="F54">
-        <v>-4.713507588162822</v>
+        <v>-4.208336011239572</v>
       </c>
       <c r="G54">
-        <v>-6.48436007734773</v>
+        <v>-7.614424728814567</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.500386329351993</v>
       </c>
       <c r="E55">
-        <v>-9.191015565045397</v>
+        <v>-11.56452011821165</v>
       </c>
       <c r="F55">
-        <v>-4.805207031285325</v>
+        <v>-4.426378879004457</v>
       </c>
       <c r="G55">
-        <v>-6.32246446884075</v>
+        <v>-7.387526558643998</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.46634059077088</v>
       </c>
       <c r="E56">
-        <v>-9.768948474852305</v>
+        <v>-11.31877794771141</v>
       </c>
       <c r="F56">
-        <v>-4.646701413861848</v>
+        <v>-4.593626257629678</v>
       </c>
       <c r="G56">
-        <v>-6.584487527182986</v>
+        <v>-7.311774655614395</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.47179028119284</v>
       </c>
       <c r="E57">
-        <v>-7.904204391025789</v>
+        <v>-10.58607085327035</v>
       </c>
       <c r="F57">
-        <v>-4.914083500872278</v>
+        <v>-4.637234831182655</v>
       </c>
       <c r="G57">
-        <v>-7.423273829377049</v>
+        <v>-7.193982134781587</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.4561423086067</v>
       </c>
       <c r="E58">
-        <v>-9.087942968156813</v>
+        <v>-11.31832057183664</v>
       </c>
       <c r="F58">
-        <v>-4.37172154103294</v>
+        <v>-4.701771278799959</v>
       </c>
       <c r="G58">
-        <v>-7.032271916824807</v>
+        <v>-6.815119992721853</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.361157740837537</v>
       </c>
       <c r="E59">
-        <v>-7.263687970432878</v>
+        <v>-9.823050153821942</v>
       </c>
       <c r="F59">
-        <v>-4.642594368278767</v>
+        <v>-4.384990330090983</v>
       </c>
       <c r="G59">
-        <v>-6.945048973501629</v>
+        <v>-6.56130708731701</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.137171014730212</v>
       </c>
       <c r="E60">
-        <v>-7.656619131604428</v>
+        <v>-10.14982936668944</v>
       </c>
       <c r="F60">
-        <v>-5.044208422708441</v>
+        <v>-4.530037462321176</v>
       </c>
       <c r="G60">
-        <v>-7.183865107613574</v>
+        <v>-7.203907150308322</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.751535101443515</v>
       </c>
       <c r="E61">
-        <v>-7.107084282299622</v>
+        <v>-10.20253627566472</v>
       </c>
       <c r="F61">
-        <v>-5.048532500551055</v>
+        <v>-4.703847167511374</v>
       </c>
       <c r="G61">
-        <v>-7.429957820820837</v>
+        <v>-7.95808584015523</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.187091236399485</v>
       </c>
       <c r="E62">
-        <v>-6.651764334724398</v>
+        <v>-9.140432510379719</v>
       </c>
       <c r="F62">
-        <v>-4.968471619437885</v>
+        <v>-4.826826592130989</v>
       </c>
       <c r="G62">
-        <v>-6.847450780458376</v>
+        <v>-7.372933673906891</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.441329974511282</v>
       </c>
       <c r="E63">
-        <v>-7.751359336318899</v>
+        <v>-10.07058107155521</v>
       </c>
       <c r="F63">
-        <v>-5.034285409590305</v>
+        <v>-4.575325964967031</v>
       </c>
       <c r="G63">
-        <v>-8.36867625066334</v>
+        <v>-7.560429731069054</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.525043141033827</v>
       </c>
       <c r="E64">
-        <v>-7.338299108183255</v>
+        <v>-8.727657576106559</v>
       </c>
       <c r="F64">
-        <v>-5.08299424124232</v>
+        <v>-4.858148820365644</v>
       </c>
       <c r="G64">
-        <v>-7.584090200038225</v>
+        <v>-7.146018951008626</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.463724605918796</v>
       </c>
       <c r="E65">
-        <v>-6.631884333830725</v>
+        <v>-9.030295494039169</v>
       </c>
       <c r="F65">
-        <v>-4.975038916207279</v>
+        <v>-4.708081781674485</v>
       </c>
       <c r="G65">
-        <v>-7.657521410644799</v>
+        <v>-7.689259610729792</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.288135281973742</v>
       </c>
       <c r="E66">
-        <v>-6.971845934534555</v>
+        <v>-9.391445824624888</v>
       </c>
       <c r="F66">
-        <v>-4.953218890450137</v>
+        <v>-4.755472680788645</v>
       </c>
       <c r="G66">
-        <v>-7.933260059156236</v>
+        <v>-7.912694950266283</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.032381831902118</v>
       </c>
       <c r="E67">
-        <v>-5.339978626552488</v>
+        <v>-9.200701970947804</v>
       </c>
       <c r="F67">
-        <v>-5.002476929690207</v>
+        <v>-4.749814931427524</v>
       </c>
       <c r="G67">
-        <v>-7.916886100919</v>
+        <v>-7.825369380031388</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.729830252855346</v>
       </c>
       <c r="E68">
-        <v>-6.528118880418967</v>
+        <v>-8.983520886013942</v>
       </c>
       <c r="F68">
-        <v>-5.275076074603469</v>
+        <v>-4.707866406149757</v>
       </c>
       <c r="G68">
-        <v>-7.090487860132891</v>
+        <v>-7.784590080078646</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.409830056295939</v>
       </c>
       <c r="E69">
-        <v>-5.781061051847596</v>
+        <v>-8.096732463461894</v>
       </c>
       <c r="F69">
-        <v>-5.409141540174749</v>
+        <v>-4.87451073330574</v>
       </c>
       <c r="G69">
-        <v>-7.348515090009227</v>
+        <v>-7.538139827953141</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.09616415458703</v>
       </c>
       <c r="E70">
-        <v>-7.198174536963911</v>
+        <v>-8.7778647674296</v>
       </c>
       <c r="F70">
-        <v>-5.324166783628173</v>
+        <v>-4.897060550744748</v>
       </c>
       <c r="G70">
-        <v>-7.107907950760536</v>
+        <v>-7.955139454625279</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.805082133293638</v>
       </c>
       <c r="E71">
-        <v>-6.949756038325138</v>
+        <v>-9.063828844065968</v>
       </c>
       <c r="F71">
-        <v>-5.713658509485279</v>
+        <v>-5.371954470728274</v>
       </c>
       <c r="G71">
-        <v>-7.214341989848105</v>
+        <v>-7.036578936571399</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.546291400488951</v>
       </c>
       <c r="E72">
-        <v>-6.280918541288258</v>
+        <v>-8.494418522341498</v>
       </c>
       <c r="F72">
-        <v>-5.677149044574293</v>
+        <v>-4.983253007373439</v>
       </c>
       <c r="G72">
-        <v>-7.191141686708892</v>
+        <v>-7.085273750908539</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.320360642910436</v>
       </c>
       <c r="E73">
-        <v>-6.297447471416254</v>
+        <v>-9.116354614080937</v>
       </c>
       <c r="F73">
-        <v>-5.69614185238568</v>
+        <v>-5.087780548095695</v>
       </c>
       <c r="G73">
-        <v>-6.647182638605704</v>
+        <v>-7.399067120393898</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.123885048204792</v>
       </c>
       <c r="E74">
-        <v>-7.054870976991182</v>
+        <v>-9.071961983383744</v>
       </c>
       <c r="F74">
-        <v>-5.491513566341729</v>
+        <v>-5.039771686899047</v>
       </c>
       <c r="G74">
-        <v>-6.875252741897175</v>
+        <v>-6.842382335237751</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.945756720976429</v>
       </c>
       <c r="E75">
-        <v>-6.582388112926888</v>
+        <v>-9.068973190538681</v>
       </c>
       <c r="F75">
-        <v>-6.080110024400918</v>
+        <v>-5.480097006796346</v>
       </c>
       <c r="G75">
-        <v>-6.079606158625356</v>
+        <v>-6.657835974151079</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.772365237541743</v>
       </c>
       <c r="E76">
-        <v>-7.13134784603272</v>
+        <v>-9.352193011926401</v>
       </c>
       <c r="F76">
-        <v>-6.339029095840647</v>
+        <v>-5.37374954289014</v>
       </c>
       <c r="G76">
-        <v>-6.238396475416498</v>
+        <v>-6.281522952156584</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.590532881556212</v>
       </c>
       <c r="E77">
-        <v>-8.423076942824659</v>
+        <v>-10.11131469525421</v>
       </c>
       <c r="F77">
-        <v>-5.459614794394726</v>
+        <v>-5.299441673389413</v>
       </c>
       <c r="G77">
-        <v>-6.521170033198886</v>
+        <v>-6.675673193516672</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.392314339411428</v>
       </c>
       <c r="E78">
-        <v>-7.972389624159281</v>
+        <v>-10.17553751363099</v>
       </c>
       <c r="F78">
-        <v>-5.949009285764257</v>
+        <v>-5.760805868583015</v>
       </c>
       <c r="G78">
-        <v>-6.383146768575592</v>
+        <v>-6.489862204033998</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.17196926267378</v>
       </c>
       <c r="E79">
-        <v>-9.196508604016701</v>
+        <v>-10.92397199830069</v>
       </c>
       <c r="F79">
-        <v>-6.229547503865948</v>
+        <v>-5.975684372869207</v>
       </c>
       <c r="G79">
-        <v>-6.480973389261055</v>
+        <v>-6.611286393323387</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.927755755774438</v>
       </c>
       <c r="E80">
-        <v>-10.35711120744254</v>
+        <v>-11.28465136758961</v>
       </c>
       <c r="F80">
-        <v>-6.024614378617768</v>
+        <v>-5.983385704613034</v>
       </c>
       <c r="G80">
-        <v>-5.371324872134903</v>
+        <v>-6.097449999082027</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.663671394777578</v>
       </c>
       <c r="E81">
-        <v>-9.825640440954329</v>
+        <v>-11.96962381751582</v>
       </c>
       <c r="F81">
-        <v>-6.197220465971698</v>
+        <v>-5.99218462316557</v>
       </c>
       <c r="G81">
-        <v>-5.693523716744471</v>
+        <v>-5.865241713866467</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.386644756633713</v>
       </c>
       <c r="E82">
-        <v>-11.96071178066873</v>
+        <v>-13.24834713695773</v>
       </c>
       <c r="F82">
-        <v>-6.359061918926249</v>
+        <v>-5.831622997848345</v>
       </c>
       <c r="G82">
-        <v>-4.917389488881116</v>
+        <v>-6.071876034791157</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.102822821414895</v>
       </c>
       <c r="E83">
-        <v>-13.61357762262436</v>
+        <v>-13.33409832076698</v>
       </c>
       <c r="F83">
-        <v>-6.464527585732174</v>
+        <v>-6.134638137057598</v>
       </c>
       <c r="G83">
-        <v>-5.808009002583548</v>
+        <v>-5.88103963717987</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.815796284732393</v>
       </c>
       <c r="E84">
-        <v>-12.05127673234813</v>
+        <v>-14.39748817267015</v>
       </c>
       <c r="F84">
-        <v>-6.828883331118732</v>
+        <v>-6.238251988534566</v>
       </c>
       <c r="G84">
-        <v>-5.499456226686855</v>
+        <v>-5.471674128521292</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.531267954608412</v>
       </c>
       <c r="E85">
-        <v>-14.08556235454781</v>
+        <v>-14.4030627241736</v>
       </c>
       <c r="F85">
-        <v>-7.122873821658186</v>
+        <v>-6.759153019885875</v>
       </c>
       <c r="G85">
-        <v>-5.582345665899127</v>
+        <v>-5.721590521826412</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.255049489513166</v>
       </c>
       <c r="E86">
-        <v>-15.17980017139124</v>
+        <v>-16.136087084539</v>
       </c>
       <c r="F86">
-        <v>-7.276543016000418</v>
+        <v>-6.729029853466773</v>
       </c>
       <c r="G86">
-        <v>-6.188387374500268</v>
+        <v>-5.049870900271671</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.994298425869647</v>
       </c>
       <c r="E87">
-        <v>-16.71669632248444</v>
+        <v>-17.8792597551556</v>
       </c>
       <c r="F87">
-        <v>-6.850114387652483</v>
+        <v>-6.535434592860708</v>
       </c>
       <c r="G87">
-        <v>-6.155255434743242</v>
+        <v>-5.712393826318317</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.75624011088062</v>
       </c>
       <c r="E88">
-        <v>-17.32393298759498</v>
+        <v>-18.06313844223705</v>
       </c>
       <c r="F88">
-        <v>-7.056000549597584</v>
+        <v>-6.536548747017473</v>
       </c>
       <c r="G88">
-        <v>-5.634145771952103</v>
+        <v>-4.984881580790238</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.550973476396582</v>
       </c>
       <c r="E89">
-        <v>-18.45688020025598</v>
+        <v>-20.28407417761089</v>
       </c>
       <c r="F89">
-        <v>-7.35588570257536</v>
+        <v>-7.026721903745636</v>
       </c>
       <c r="G89">
-        <v>-5.424978883689871</v>
+        <v>-5.76729922408713</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.387456501131427</v>
       </c>
       <c r="E90">
-        <v>-20.74451582928879</v>
+        <v>-22.02343387311303</v>
       </c>
       <c r="F90">
-        <v>-6.937367568740459</v>
+        <v>-7.008745502737484</v>
       </c>
       <c r="G90">
-        <v>-6.179389311724528</v>
+        <v>-5.587798134402306</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.276080758635853</v>
       </c>
       <c r="E91">
-        <v>-22.87169856728183</v>
+        <v>-23.25179603311564</v>
       </c>
       <c r="F91">
-        <v>-7.611030732127935</v>
+        <v>-6.91363111499694</v>
       </c>
       <c r="G91">
-        <v>-4.763323320574513</v>
+        <v>-6.084489213295781</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.227639730727234</v>
       </c>
       <c r="E92">
-        <v>-25.28731340024541</v>
+        <v>-25.60006792911115</v>
       </c>
       <c r="F92">
-        <v>-7.499597506552241</v>
+        <v>-7.049637859576682</v>
       </c>
       <c r="G92">
-        <v>-6.446163002915618</v>
+        <v>-6.245825339606623</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.252622203942306</v>
       </c>
       <c r="E93">
-        <v>-26.69143469343372</v>
+        <v>-27.28498178161907</v>
       </c>
       <c r="F93">
-        <v>-7.400824219993532</v>
+        <v>-7.352152250690943</v>
       </c>
       <c r="G93">
-        <v>-7.08477054798657</v>
+        <v>-6.134521488030786</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.356776577362593</v>
       </c>
       <c r="E94">
-        <v>-29.79123855032018</v>
+        <v>-29.37890287802577</v>
       </c>
       <c r="F94">
-        <v>-7.923701735967921</v>
+        <v>-7.141082165539122</v>
       </c>
       <c r="G94">
-        <v>-6.491457886983927</v>
+        <v>-6.815960871288828</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.542673866042291</v>
       </c>
       <c r="E95">
-        <v>-30.37611361078085</v>
+        <v>-31.57007295374719</v>
       </c>
       <c r="F95">
-        <v>-7.272268640201973</v>
+        <v>-7.098050964065896</v>
       </c>
       <c r="G95">
-        <v>-7.494738575933296</v>
+        <v>-7.194263531152425</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.812044612184173</v>
       </c>
       <c r="E96">
-        <v>-33.09686155085527</v>
+        <v>-33.46573292962407</v>
       </c>
       <c r="F96">
-        <v>-7.487795341980855</v>
+        <v>-7.292668844230716</v>
       </c>
       <c r="G96">
-        <v>-7.667813896726393</v>
+        <v>-7.432391071792201</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.151908418500483</v>
       </c>
       <c r="E97">
-        <v>-35.30881279379788</v>
+        <v>-36.354455556065</v>
       </c>
       <c r="F97">
-        <v>-7.581071996638288</v>
+        <v>-7.532345769270815</v>
       </c>
       <c r="G97">
-        <v>-7.96162812388225</v>
+        <v>-7.908705742891462</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.557154291821265</v>
       </c>
       <c r="E98">
-        <v>-37.56970325534139</v>
+        <v>-38.79863826730598</v>
       </c>
       <c r="F98">
-        <v>-7.155349137317538</v>
+        <v>-7.343316469788982</v>
       </c>
       <c r="G98">
-        <v>-8.539669238312236</v>
+        <v>-8.792631333513485</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.992638239592471</v>
       </c>
       <c r="E99">
-        <v>-41.38146926723979</v>
+        <v>-40.59696548709899</v>
       </c>
       <c r="F99">
-        <v>-8.303937698649845</v>
+        <v>-7.329637638866553</v>
       </c>
       <c r="G99">
-        <v>-8.702028323194712</v>
+        <v>-9.311403751153899</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.45757432790874</v>
       </c>
       <c r="E100">
-        <v>-42.95424451789577</v>
+        <v>-42.88098286539967</v>
       </c>
       <c r="F100">
-        <v>-7.363625139219716</v>
+        <v>-7.27003370494922</v>
       </c>
       <c r="G100">
-        <v>-9.363094609204079</v>
+        <v>-9.262076622618759</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.890624594221713</v>
       </c>
       <c r="E101">
-        <v>-45.06125969689564</v>
+        <v>-45.54061904874058</v>
       </c>
       <c r="F101">
-        <v>-7.648123781874192</v>
+        <v>-7.313810851268666</v>
       </c>
       <c r="G101">
-        <v>-8.677331653471748</v>
+        <v>-9.279099447781691</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.33744030997863</v>
       </c>
       <c r="E102">
-        <v>-47.04553511639162</v>
+        <v>-47.77716443401886</v>
       </c>
       <c r="F102">
-        <v>-7.579266569883886</v>
+        <v>-7.130383800531966</v>
       </c>
       <c r="G102">
-        <v>-10.47288216924288</v>
+        <v>-10.53279642241261</v>
       </c>
     </row>
   </sheetData>
